--- a/files/excel-mastery-4-3.xlsx
+++ b/files/excel-mastery-4-3.xlsx
@@ -541,7 +541,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
     <xf numFmtId="38" fontId="10" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -549,8 +549,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="190">
+  <cellXfs count="192">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -647,9 +650,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -704,21 +704,12 @@
     <xf numFmtId="165" fontId="9" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="3" fontId="6" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="3" fontId="6" fillId="5" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="3" fontId="6" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -731,29 +722,8 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="13" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center"/>
@@ -869,249 +839,293 @@
     <xf numFmtId="0" fontId="27" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="16" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="16" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="16" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="24" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="24" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="24" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="16" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="25" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="17" fillId="4" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="17" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="12" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="17" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="28" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="28" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="22" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="13" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="16" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="28" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="28" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="28" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="23" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="23" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="16" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="16" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="16" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="24" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="24" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="24" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="24" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="16" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="25" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="17" fillId="4" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="17" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="12" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="17" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="28" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="28" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="22" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="13" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="16" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="28" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="28" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="28" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="23" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="23" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="38" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="22" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="4">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
     <cellStyle name="桁区切り" xfId="1" builtinId="6"/>
     <cellStyle name="標準 2" xfId="2"/>
+    <cellStyle name="パーセント" xfId="3" builtinId="5"/>
   </cellStyles>
   <dxfs count="6">
     <dxf>
@@ -1551,149 +1565,149 @@
   <dimension ref="B2:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13"/>
   <cols>
-    <col width="2.36328125" customWidth="1" style="158" min="1" max="3"/>
-    <col width="30" customWidth="1" style="158" min="4" max="4"/>
-    <col width="14" customWidth="1" style="158" min="5" max="5"/>
-    <col width="22" customWidth="1" style="158" min="6" max="6"/>
-    <col width="10" customWidth="1" style="158" min="7" max="7"/>
-    <col width="30" customWidth="1" style="158" min="8" max="8"/>
+    <col width="2.36328125" customWidth="1" min="1" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="2" ht="19.5" customHeight="1" s="158">
-      <c r="B2" s="75" t="inlineStr">
+    <row r="2" ht="19.5" customHeight="1">
+      <c r="B2" s="64" t="inlineStr">
         <is>
           <t>4-3. 常識との整合性を確認する</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="13.5" customHeight="1" s="158"/>
-    <row r="4" ht="13.5" customHeight="1" s="158">
+    <row r="3" ht="13.5" customHeight="1"/>
+    <row r="4" ht="13.5" customHeight="1">
       <c r="D4" s="3" t="inlineStr">
         <is>
           <t>数式が正しくても前提が非常識なら結論は誤り。「桁」と「率」を常識レンジと突き合わせる。</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="13.5" customHeight="1" s="158">
-      <c r="D5" s="77" t="inlineStr">
+    <row r="5" ht="13.5" customHeight="1">
+      <c r="D5" s="66" t="inlineStr">
         <is>
           <t>常識レンジとの照合</t>
         </is>
       </c>
-      <c r="E5" s="78" t="n"/>
-      <c r="F5" s="78" t="n"/>
-      <c r="G5" s="78" t="n"/>
-      <c r="H5" s="78" t="n"/>
+      <c r="E5" s="67" t="n"/>
+      <c r="F5" s="67" t="n"/>
+      <c r="G5" s="67" t="n"/>
+      <c r="H5" s="67" t="n"/>
     </row>
-    <row r="6" ht="13.5" customHeight="1" s="158"/>
-    <row r="7" ht="13.5" customHeight="1" s="158">
-      <c r="D7" s="168" t="inlineStr">
+    <row r="6" ht="13.5" customHeight="1"/>
+    <row r="7" ht="13.5" customHeight="1">
+      <c r="D7" s="68" t="inlineStr">
         <is>
           <t>指標</t>
         </is>
       </c>
-      <c r="E7" s="168" t="inlineStr">
+      <c r="E7" s="68" t="inlineStr">
         <is>
           <t>値</t>
         </is>
       </c>
-      <c r="F7" s="168" t="inlineStr">
+      <c r="F7" s="68" t="inlineStr">
         <is>
           <t>常識レンジ</t>
         </is>
       </c>
-      <c r="G7" s="168" t="inlineStr">
+      <c r="G7" s="68" t="inlineStr">
         <is>
           <t>判定</t>
         </is>
       </c>
-      <c r="H7" s="168" t="inlineStr">
+      <c r="H7" s="68" t="inlineStr">
         <is>
           <t>コメント</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="13.5" customHeight="1" s="158">
-      <c r="D8" s="80" t="inlineStr">
+    <row r="8" ht="13.5" customHeight="1">
+      <c r="D8" s="69" t="inlineStr">
         <is>
           <t>1日あたり販売室数（客室10室）</t>
         </is>
       </c>
-      <c r="E8" s="81" t="n">
+      <c r="E8" s="70" t="n">
         <v>15</v>
       </c>
-      <c r="F8" s="88" t="inlineStr">
+      <c r="F8" s="77" t="inlineStr">
         <is>
           <t>0〜10室</t>
         </is>
       </c>
-      <c r="G8" s="102">
+      <c r="G8" s="91">
         <f>IF(E8&lt;=10,"OK","異常")</f>
         <v/>
       </c>
-      <c r="H8" s="103" t="inlineStr">
+      <c r="H8" s="92" t="inlineStr">
         <is>
           <t>客室数を超えて販売している</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="13.5" customHeight="1" s="158">
-      <c r="D9" s="83" t="inlineStr">
+    <row r="9" ht="13.5" customHeight="1">
+      <c r="D9" s="72" t="inlineStr">
         <is>
           <t>料理原価率</t>
         </is>
       </c>
-      <c r="E9" s="189" t="n">
+      <c r="E9" s="191" t="n">
         <v>0.05</v>
       </c>
-      <c r="F9" s="90" t="inlineStr">
+      <c r="F9" s="79" t="inlineStr">
         <is>
           <t>20%〜40%</t>
         </is>
       </c>
-      <c r="G9" s="104">
+      <c r="G9" s="93">
         <f>IF(AND(E9&gt;=0.2,E9&lt;=0.4),"OK","異常")</f>
         <v/>
       </c>
-      <c r="H9" s="105" t="inlineStr">
+      <c r="H9" s="94" t="inlineStr">
         <is>
           <t>5%は低すぎ（仕入計上漏れの疑い）</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="13.5" customHeight="1" s="158">
-      <c r="D10" s="85" t="inlineStr">
+    <row r="10" ht="13.5" customHeight="1">
+      <c r="D10" s="74" t="inlineStr">
         <is>
           <t>正社員1人あたり人件費（月）</t>
         </is>
       </c>
-      <c r="E10" s="86" t="n">
+      <c r="E10" s="75" t="n">
         <v>50000</v>
       </c>
-      <c r="F10" s="94" t="inlineStr">
+      <c r="F10" s="83" t="inlineStr">
         <is>
           <t>25〜40万円/月</t>
         </is>
       </c>
-      <c r="G10" s="106">
+      <c r="G10" s="95">
         <f>IF(AND(E10&gt;=250000,E10&lt;=400000),"OK","異常")</f>
         <v/>
       </c>
-      <c r="H10" s="107" t="inlineStr">
+      <c r="H10" s="96" t="inlineStr">
         <is>
           <t>月5万円は非現実的（年額混同の疑い）</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="13.5" customHeight="1" s="158"/>
-    <row r="12" ht="13.5" customHeight="1" s="158">
-      <c r="D12" s="76" t="inlineStr">
+    <row r="11" ht="13.5" customHeight="1"/>
+    <row r="12" ht="13.5" customHeight="1">
+      <c r="D12" s="65" t="inlineStr">
         <is>
           <t>すべて意図的に「異常」になる例です。IF＋AND で常識レンジ内かを自動判定できます。</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="13.5" customHeight="1" s="158"/>
+    <row r="13" ht="13.5" customHeight="1"/>
   </sheetData>
   <conditionalFormatting sqref="G8:G10">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="1">

--- a/files/excel-mastery-4-3.xlsx
+++ b/files/excel-mastery-4-3.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-1605" yWindow="-16320" windowWidth="29040" windowHeight="16440" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="280" windowWidth="17320" windowHeight="10400" tabRatio="773" firstSheet="2" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="4-3_常識チェック" sheetId="1" state="visible" r:id="rId1"/>
@@ -553,7 +553,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="192">
+  <cellXfs count="193">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -1049,74 +1049,77 @@
     <xf numFmtId="3" fontId="23" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="13" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="13" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="13" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="165" fontId="22" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -1657,7 +1660,7 @@
           <t>料理原価率</t>
         </is>
       </c>
-      <c r="E9" s="191" t="n">
+      <c r="E9" s="192" t="n">
         <v>0.05</v>
       </c>
       <c r="F9" s="79" t="inlineStr">
